--- a/site/Integration-Schedule-Setup-Guide/headings.xlsx
+++ b/site/Integration-Schedule-Setup-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,20 +661,42 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Disable or Enable Scheduled Runs</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>h_01KG4A9CZRZQ493NBRS1AWBHQW</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Schedule-Setup-Guide/#h_01KG4A9CZRZQ493NBRS1AWBHQW</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>References</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>h_01H02H9WB603XRNADRN1EK60SB</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Schedule-Setup-Guide/#h_01H02H9WB603XRNADRN1EK60SB</t>
         </is>
